--- a/Test/Results.xlsx
+++ b/Test/Results.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Repos\Bread_porosity_scan\Pictures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Repos\Bread_porosity_scan\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85502002-40A8-4061-9BFE-B046946E06DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB435783-8D49-4EDB-B750-269B688A7CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{2573E81A-6BAB-44BA-8423-E24BE3525652}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{2573E81A-6BAB-44BA-8423-E24BE3525652}"/>
   </bookViews>
   <sheets>
-    <sheet name="6_BreadCrumbPorosity" sheetId="1" r:id="rId1"/>
+    <sheet name="6_BreadCrumbPorosity" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="6_BreadCrumbPorosity_new_model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="37">
   <si>
     <t>N</t>
   </si>
@@ -331,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -369,11 +367,40 @@
     <xf numFmtId="2" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     </dxf>
@@ -993,6 +1020,789 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-E8C3-4BAE-8E3F-CA281BE06534}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1149510992"/>
+        <c:axId val="1149511472"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1149510992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1149511472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1149511472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1149510992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Coefficient of Variation (%) by Test</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$W$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CV% 2D Porosity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$K$3:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Flour</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$W$3:$W$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>7.232401157183603E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7518681805250496</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.511273347306791</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5714498010925864</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5333512458473111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.563623225152128</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.068736941422111</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.7847902736982562</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.480118166365644</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9E3-4252-9997-31FA57538341}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$X$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CV% 3D Vol.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$K$3:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Flour</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$X$3:$X$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>7.2476556434332276E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7562282208062985</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.524491073620368</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5781779742657589</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5256819752435886</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.578261043300282</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.061187405455094</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.7556175243229086</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.492669865338382</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E9E3-4252-9997-31FA57538341}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$Y$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CV% Cell Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$K$3:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Flour</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$Y$3:$Y$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.4686524553281315</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5087550588579073</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.872445106277837</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9566959766801109</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.6813886922309762</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28.102877981579343</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1442125095943672</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.1923590109712014</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.6819029731657533</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E9E3-4252-9997-31FA57538341}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$Z$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CV% Cell Density</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$K$3:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Flour</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$Z$3:$Z$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.64677268907084617</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2168598786360834</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.389850327924286</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8455220837984889</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1602809914205197</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.7339104816277766</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9972099804446533</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1927278368367191</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5585532305554466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E9E3-4252-9997-31FA57538341}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$AA$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CV% Mean Cell Area</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$K$3:$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Flour</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20% BSG+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20% BSG_fraction+70ppmE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20% BSG+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20% BSG_fraction+140ppmE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'6_BreadCrumbPorosity_new_model'!$AA$3:$AA$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.71657862467477029</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7349689603934855</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.552498712404002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.27932391576592</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.5748498347329436</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.665688588560979</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.52285302091623</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1762874902528893</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.910522359922904</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-E9E3-4252-9997-31FA57538341}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1238,7 +2048,552 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1786,252 +3141,80 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="0_Summary"/>
-      <sheetName val="1_RawMaterial"/>
-      <sheetName val="2_Rheology"/>
-      <sheetName val="3_BreadFormulation&amp;measurements"/>
-      <sheetName val="4_BreadComposition"/>
-      <sheetName val="5_Sensorial"/>
-      <sheetName val="6_BreadCrumbPorosity"/>
-      <sheetName val="Extra_RecipientsWeight"/>
-      <sheetName val="Hoja1"/>
-      <sheetName val="Hoja2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="2">
-          <cell r="W2" t="str">
-            <v>CV% 2D Porosity</v>
-          </cell>
-          <cell r="X2" t="str">
-            <v>CV% 3D Vol.</v>
-          </cell>
-          <cell r="Y2" t="str">
-            <v>CV% Cell Count</v>
-          </cell>
-          <cell r="Z2" t="str">
-            <v>CV% Cell Density</v>
-          </cell>
-          <cell r="AA2" t="str">
-            <v>CV% Mean Cell Area</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="K3" t="str">
-            <v>Flour</v>
-          </cell>
-          <cell r="W3">
-            <v>8.7605038181842723</v>
-          </cell>
-          <cell r="X3">
-            <v>8.728171032123754</v>
-          </cell>
-          <cell r="Y3">
-            <v>10.218667718673322</v>
-          </cell>
-          <cell r="Z3">
-            <v>11.154189749771778</v>
-          </cell>
-          <cell r="AA3">
-            <v>18.779958375860421</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4" t="str">
-            <v>10% BSG+70ppmE</v>
-          </cell>
-          <cell r="W4">
-            <v>9.3443425301005441</v>
-          </cell>
-          <cell r="X4">
-            <v>9.3585436585657487</v>
-          </cell>
-          <cell r="Y4">
-            <v>11.91511110594289</v>
-          </cell>
-          <cell r="Z4">
-            <v>8.3739157172149827</v>
-          </cell>
-          <cell r="AA4">
-            <v>16.210005414204957</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5" t="str">
-            <v>20% BSG+70ppmE</v>
-          </cell>
-          <cell r="W5">
-            <v>20.046714329921485</v>
-          </cell>
-          <cell r="X5">
-            <v>19.891779350413913</v>
-          </cell>
-          <cell r="Y5">
-            <v>12.246595592576341</v>
-          </cell>
-          <cell r="Z5">
-            <v>10.37014857850939</v>
-          </cell>
-          <cell r="AA5">
-            <v>12.458132647548583</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6" t="str">
-            <v>10% BSG_fraction+70ppmE</v>
-          </cell>
-          <cell r="W6">
-            <v>17.465307376617947</v>
-          </cell>
-          <cell r="X6">
-            <v>17.462063974927851</v>
-          </cell>
-          <cell r="Y6">
-            <v>9.7940489275820912</v>
-          </cell>
-          <cell r="Z6">
-            <v>10.463435562540015</v>
-          </cell>
-          <cell r="AA6">
-            <v>28.003502508052296</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="K7" t="str">
-            <v>20% BSG_fraction+70ppmE</v>
-          </cell>
-          <cell r="W7">
-            <v>5.2759917540609971</v>
-          </cell>
-          <cell r="X7">
-            <v>5.2517557470497014</v>
-          </cell>
-          <cell r="Y7">
-            <v>4.3372972312534275</v>
-          </cell>
-          <cell r="Z7">
-            <v>0.78467223076964387</v>
-          </cell>
-          <cell r="AA7">
-            <v>4.373523954074046</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="K8" t="str">
-            <v>10% BSG+140ppmE</v>
-          </cell>
-          <cell r="W8">
-            <v>1.7255583191757846E-14</v>
-          </cell>
-          <cell r="X8">
-            <v>0.19527066601678453</v>
-          </cell>
-          <cell r="Y8">
-            <v>6.1172329227962372</v>
-          </cell>
-          <cell r="Z8">
-            <v>2.9203410988020684</v>
-          </cell>
-          <cell r="AA8">
-            <v>2.9727542820950421</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="K9" t="str">
-            <v>20% BSG+140ppmE</v>
-          </cell>
-          <cell r="W9">
-            <v>12.371989670709823</v>
-          </cell>
-          <cell r="X9">
-            <v>12.294773254145213</v>
-          </cell>
-          <cell r="Y9">
-            <v>3.0140379541257212</v>
-          </cell>
-          <cell r="Z9">
-            <v>1.0856941619958795</v>
-          </cell>
-          <cell r="AA9">
-            <v>13.380166882340792</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="K10" t="str">
-            <v>10% BSG_fraction+140ppmE</v>
-          </cell>
-          <cell r="W10">
-            <v>1.9521560244925029</v>
-          </cell>
-          <cell r="X10">
-            <v>2.226780544724841</v>
-          </cell>
-          <cell r="Y10">
-            <v>5.1081068447543849</v>
-          </cell>
-          <cell r="Z10">
-            <v>4.1328562447468675</v>
-          </cell>
-          <cell r="AA10">
-            <v>3.1169929166978561</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="K11" t="str">
-            <v>20% BSG_fraction+140ppmE</v>
-          </cell>
-          <cell r="W11">
-            <v>2.8758166424615137</v>
-          </cell>
-          <cell r="X11">
-            <v>3.2203602961288311</v>
-          </cell>
-          <cell r="Y11">
-            <v>4.4508018514377214</v>
-          </cell>
-          <cell r="Z11">
-            <v>1.3853959807052405</v>
-          </cell>
-          <cell r="AA11">
-            <v>3.341011710031335</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>825500</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BAC7058-61D0-4D0F-9250-48353D3BE7E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{58B4A7E8-75AA-4D6F-8F60-1E8465239C7F}" name="Tabla8" displayName="Tabla8" ref="A1:I28" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{58B4A7E8-75AA-4D6F-8F60-1E8465239C7F}" name="Tabla8" displayName="Tabla8" ref="A1:I28" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:I28" xr:uid="{1E558C18-AFC9-4555-9161-4AEE8E834711}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{1B9D30CB-8EBD-4BDE-AA0C-66BF7E990EC0}" name="N"/>
     <tableColumn id="9" xr3:uid="{6A6D209E-2483-45EE-8BF3-87559CC9A35C}" name="Name"/>
     <tableColumn id="2" xr3:uid="{2C509A9F-51EC-42E2-A4D4-874A41911E2C}" name="Method of Measurement"/>
-    <tableColumn id="3" xr3:uid="{DA565457-82B1-465A-BFC4-7AAF53FC98AC}" name="2D Porosity / Void Fraction (%) " dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{793DA5A1-A2CB-41C5-9A36-6BEB262AA0ED}" name="3D Corrected Estimated Vol. (%)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{DA565457-82B1-465A-BFC4-7AAF53FC98AC}" name="2D Porosity / Void Fraction (%) " dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{793DA5A1-A2CB-41C5-9A36-6BEB262AA0ED}" name="3D Corrected Estimated Vol. (%)" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{B65E0009-0EDA-440E-B3FB-3732335DECF8}" name="Cell Count (valid pores)"/>
     <tableColumn id="6" xr3:uid="{B71523B2-111F-4569-A7CD-D384B39D8C92}" name="Cell Density (cells/cm²)"/>
     <tableColumn id="7" xr3:uid="{135314BA-E2FB-4401-AA5A-C90DB524A79B}" name="Mean Cell Area (mm² per pore)"/>
-    <tableColumn id="10" xr3:uid="{B519A9D0-6A85-4411-965C-0B258D5877B6}" name="Date" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{B519A9D0-6A85-4411-965C-0B258D5877B6}" name="Date" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{303B002E-A198-4A58-B9FC-63BC84879F82}" name="Tabla83" displayName="Tabla83" ref="A1:I28" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:I28" xr:uid="{1E558C18-AFC9-4555-9161-4AEE8E834711}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{F14797C7-43D5-40AF-9064-C40813596BD7}" name="N"/>
+    <tableColumn id="9" xr3:uid="{94C799DF-F132-45E1-BDCD-597FE63E261F}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{A8F50B1E-D1BF-4C5B-9BC2-1599DD967F4A}" name="Method of Measurement"/>
+    <tableColumn id="3" xr3:uid="{1092342A-54FE-4839-8607-F2DF96FF3A39}" name="2D Porosity / Void Fraction (%) " dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{17D464B4-C8C2-4A4A-B729-032EACA41030}" name="3D Corrected Estimated Vol. (%)" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{783B967B-ED2A-4A17-B3E9-3C33C2F2F9B3}" name="Cell Count (valid pores)"/>
+    <tableColumn id="6" xr3:uid="{62DAA709-95F2-4853-BF5F-CA565D1C7A84}" name="Cell Density (cells/cm²)"/>
+    <tableColumn id="7" xr3:uid="{FE1D2B82-50F0-4E7F-8AAD-E78A8D2EAB8D}" name="Mean Cell Area (mm² per pore)"/>
+    <tableColumn id="10" xr3:uid="{80867C2D-DE14-4D65-B0DE-32FFF3EF97F1}" name="Date" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3799,4 +4982,1485 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A5E115-694F-4B08-92E4-BF58768FE2D3}">
+  <dimension ref="A1:AA28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
+    <col min="3" max="8" width="13.7265625" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="23">
+        <v>41.45</v>
+      </c>
+      <c r="E2" s="23">
+        <v>62.17</v>
+      </c>
+      <c r="F2">
+        <v>822</v>
+      </c>
+      <c r="G2">
+        <v>11.115</v>
+      </c>
+      <c r="H2">
+        <v>3.7288999999999999</v>
+      </c>
+      <c r="I2" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="23">
+        <v>26.25</v>
+      </c>
+      <c r="E3" s="23">
+        <v>39.380000000000003</v>
+      </c>
+      <c r="F3">
+        <v>569</v>
+      </c>
+      <c r="G3">
+        <v>7.6379999999999999</v>
+      </c>
+      <c r="H3">
+        <v>3.4373999999999998</v>
+      </c>
+      <c r="I3" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="12">
+        <f>AVERAGEIF($B$2:$B$28,$K3,D$2:D$28)</f>
+        <v>41.48</v>
+      </c>
+      <c r="M3" s="12" cm="1">
+        <f t="array" ref="M3">STDEV(IF($B$2:$B$28=$K3,D$2:D$28))</f>
+        <v>2.9999999999997584E-2</v>
+      </c>
+      <c r="N3" s="12">
+        <f>AVERAGEIF($B$2:$B$28,$K3,E$2:E$28)</f>
+        <v>62.216666666666669</v>
+      </c>
+      <c r="O3" s="12" cm="1">
+        <f t="array" ref="O3">STDEV(IF($B$2:$B$28=$K3,E$2:E$28))</f>
+        <v>4.5092497528227068E-2</v>
+      </c>
+      <c r="P3" s="13">
+        <f>AVERAGEIF($B$2:$B$28,$K3,F$2:F$28)</f>
+        <v>812.33333333333337</v>
+      </c>
+      <c r="Q3" s="13" cm="1">
+        <f t="array" ref="Q3">STDEV(IF($B$2:$B$28=$K3,F$2:F$28))</f>
+        <v>11.930353445448855</v>
+      </c>
+      <c r="R3" s="14">
+        <f>AVERAGEIF($B$2:$B$28,$K3,G$2:G$28)</f>
+        <v>11.033333333333333</v>
+      </c>
+      <c r="S3" s="14" cm="1">
+        <f t="array" ref="S3">STDEV(IF($B$2:$B$28=$K3,G$2:G$28))</f>
+        <v>7.1360586694150033E-2</v>
+      </c>
+      <c r="T3" s="14">
+        <f>AVERAGEIF($B$2:$B$28,$K3,H$2:H$28)</f>
+        <v>3.7596000000000003</v>
+      </c>
+      <c r="U3" s="14" cm="1">
+        <f t="array" ref="U3">STDEV(IF($B$2:$B$28=$K3,H$2:H$28))</f>
+        <v>2.6940489973272669E-2</v>
+      </c>
+      <c r="W3" s="15">
+        <f>IF(L3=0,0,M3/L3*100)</f>
+        <v>7.232401157183603E-2</v>
+      </c>
+      <c r="X3" s="15">
+        <f>IF(N3=0,0,O3/N3*100)</f>
+        <v>7.2476556434332276E-2</v>
+      </c>
+      <c r="Y3" s="15">
+        <f>IF(P3=0,0,Q3/P3*100)</f>
+        <v>1.4686524553281315</v>
+      </c>
+      <c r="Z3" s="15">
+        <f>IF(R3=0,0,S3/R3*100)</f>
+        <v>0.64677268907084617</v>
+      </c>
+      <c r="AA3" s="16">
+        <f>IF(T3=0,0,U3/T3*100)</f>
+        <v>0.71657862467477029</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="23">
+        <v>14.95</v>
+      </c>
+      <c r="E4" s="23">
+        <v>22.42</v>
+      </c>
+      <c r="F4">
+        <v>276</v>
+      </c>
+      <c r="G4">
+        <v>4.2729999999999997</v>
+      </c>
+      <c r="H4">
+        <v>3.4982000000000002</v>
+      </c>
+      <c r="I4" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="12">
+        <f t="shared" ref="L4:L11" si="0">AVERAGEIF($B$2:$B$28,$K4,D$2:D$28)</f>
+        <v>25.733333333333334</v>
+      </c>
+      <c r="M4" s="12" cm="1">
+        <f t="array" ref="M4">STDEV(IF($B$2:$B$28=$K4,D$2:D$28))</f>
+        <v>0.45081407845511279</v>
+      </c>
+      <c r="N4" s="12">
+        <f t="shared" ref="N4:N11" si="1">AVERAGEIF($B$2:$B$28,$K4,E$2:E$28)</f>
+        <v>38.603333333333332</v>
+      </c>
+      <c r="O4" s="12" cm="1">
+        <f t="array" ref="O4">STDEV(IF($B$2:$B$28=$K4,E$2:E$28))</f>
+        <v>0.67796263417192471</v>
+      </c>
+      <c r="P4" s="13">
+        <f t="shared" ref="P4:P11" si="2">AVERAGEIF($B$2:$B$28,$K4,F$2:F$28)</f>
+        <v>574</v>
+      </c>
+      <c r="Q4" s="13" cm="1">
+        <f t="array" ref="Q4">STDEV(IF($B$2:$B$28=$K4,F$2:F$28))</f>
+        <v>8.6602540378443873</v>
+      </c>
+      <c r="R4" s="14">
+        <f t="shared" ref="R4:R11" si="3">AVERAGEIF($B$2:$B$28,$K4,G$2:G$28)</f>
+        <v>7.6126666666666667</v>
+      </c>
+      <c r="S4" s="14" cm="1">
+        <f t="array" ref="S4">STDEV(IF($B$2:$B$28=$K4,G$2:G$28))</f>
+        <v>9.2635486360969577E-2</v>
+      </c>
+      <c r="T4" s="14">
+        <f t="shared" ref="T4:T11" si="4">AVERAGEIF($B$2:$B$28,$K4,H$2:H$28)</f>
+        <v>3.3809</v>
+      </c>
+      <c r="U4" s="14" cm="1">
+        <f t="array" ref="U4">STDEV(IF($B$2:$B$28=$K4,H$2:H$28))</f>
+        <v>5.8657565581943356E-2</v>
+      </c>
+      <c r="W4" s="15">
+        <f t="shared" ref="W4:W11" si="5">IF(L4=0,0,M4/L4*100)</f>
+        <v>1.7518681805250496</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" ref="X4:X11" si="6">IF(N4=0,0,O4/N4*100)</f>
+        <v>1.7562282208062985</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" ref="Y4:Y11" si="7">IF(P4=0,0,Q4/P4*100)</f>
+        <v>1.5087550588579073</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" ref="Z4:Z11" si="8">IF(R4=0,0,S4/R4*100)</f>
+        <v>1.2168598786360834</v>
+      </c>
+      <c r="AA4" s="16">
+        <f t="shared" ref="AA4:AA11" si="9">IF(T4=0,0,U4/T4*100)</f>
+        <v>1.7349689603934855</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="23">
+        <v>28.16</v>
+      </c>
+      <c r="E5" s="23">
+        <v>42.24</v>
+      </c>
+      <c r="F5">
+        <v>633</v>
+      </c>
+      <c r="G5">
+        <v>8.1</v>
+      </c>
+      <c r="H5">
+        <v>3.4761000000000002</v>
+      </c>
+      <c r="I5" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="12">
+        <f t="shared" si="0"/>
+        <v>19.66333333333333</v>
+      </c>
+      <c r="M5" s="12" cm="1">
+        <f t="array" ref="M5">STDEV(IF($B$2:$B$28=$K5,D$2:D$28))</f>
+        <v>5.4096333825254241</v>
+      </c>
+      <c r="N5" s="12">
+        <f t="shared" si="1"/>
+        <v>29.49666666666667</v>
+      </c>
+      <c r="O5" s="12" cm="1">
+        <f t="array" ref="O5">STDEV(IF($B$2:$B$28=$K5,E$2:E$28))</f>
+        <v>8.1188073836822223</v>
+      </c>
+      <c r="P5" s="13">
+        <f t="shared" si="2"/>
+        <v>386.66666666666669</v>
+      </c>
+      <c r="Q5" s="13" cm="1">
+        <f t="array" ref="Q5">STDEV(IF($B$2:$B$28=$K5,F$2:F$28))</f>
+        <v>96.173454410940977</v>
+      </c>
+      <c r="R5" s="14">
+        <f t="shared" si="3"/>
+        <v>6.0316666666666663</v>
+      </c>
+      <c r="S5" s="14" cm="1">
+        <f t="array" ref="S5">STDEV(IF($B$2:$B$28=$K5,G$2:G$28))</f>
+        <v>1.5314311389459663</v>
+      </c>
+      <c r="T5" s="14">
+        <f t="shared" si="4"/>
+        <v>3.2995999999999999</v>
+      </c>
+      <c r="U5" s="14" cm="1">
+        <f t="array" ref="U5">STDEV(IF($B$2:$B$28=$K5,H$2:H$28))</f>
+        <v>0.61215824751448245</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" si="5"/>
+        <v>27.511273347306791</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" si="6"/>
+        <v>27.524491073620368</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" si="7"/>
+        <v>24.872445106277837</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" si="8"/>
+        <v>25.389850327924286</v>
+      </c>
+      <c r="AA5" s="16">
+        <f t="shared" si="9"/>
+        <v>18.552498712404002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="23">
+        <v>23.27</v>
+      </c>
+      <c r="E6" s="23">
+        <v>34.909999999999997</v>
+      </c>
+      <c r="F6">
+        <v>602</v>
+      </c>
+      <c r="G6">
+        <v>9.6460000000000008</v>
+      </c>
+      <c r="H6">
+        <v>2.4125000000000001</v>
+      </c>
+      <c r="I6" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" si="0"/>
+        <v>27.823333333333334</v>
+      </c>
+      <c r="M6" s="12" cm="1">
+        <f t="array" ref="M6">STDEV(IF($B$2:$B$28=$K6,D$2:D$28))</f>
+        <v>1.8283963829906609</v>
+      </c>
+      <c r="N6" s="12">
+        <f t="shared" si="1"/>
+        <v>41.733333333333334</v>
+      </c>
+      <c r="O6" s="12" cm="1">
+        <f t="array" ref="O6">STDEV(IF($B$2:$B$28=$K6,E$2:E$28))</f>
+        <v>2.7452929412602436</v>
+      </c>
+      <c r="P6" s="13">
+        <f t="shared" si="2"/>
+        <v>640.33333333333337</v>
+      </c>
+      <c r="Q6" s="13" cm="1">
+        <f t="array" ref="Q6">STDEV(IF($B$2:$B$28=$K6,F$2:F$28))</f>
+        <v>57.352709904008314</v>
+      </c>
+      <c r="R6" s="14">
+        <f t="shared" si="3"/>
+        <v>8.1276666666666681</v>
+      </c>
+      <c r="S6" s="14" cm="1">
+        <f t="array" ref="S6">STDEV(IF($B$2:$B$28=$K6,G$2:G$28))</f>
+        <v>0.47510454989752859</v>
+      </c>
+      <c r="T6" s="14">
+        <f t="shared" si="4"/>
+        <v>3.4394666666666667</v>
+      </c>
+      <c r="U6" s="14" cm="1">
+        <f t="array" ref="U6">STDEV(IF($B$2:$B$28=$K6,H$2:H$28))</f>
+        <v>0.42234325297479691</v>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" si="5"/>
+        <v>6.5714498010925864</v>
+      </c>
+      <c r="X6" s="15">
+        <f t="shared" si="6"/>
+        <v>6.5781779742657589</v>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" si="7"/>
+        <v>8.9566959766801109</v>
+      </c>
+      <c r="Z6" s="15">
+        <f t="shared" si="8"/>
+        <v>5.8455220837984889</v>
+      </c>
+      <c r="AA6" s="16">
+        <f t="shared" si="9"/>
+        <v>12.27932391576592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="23">
+        <v>27.27</v>
+      </c>
+      <c r="E7" s="23">
+        <v>40.909999999999997</v>
+      </c>
+      <c r="F7">
+        <v>431</v>
+      </c>
+      <c r="G7">
+        <v>5.1589999999999998</v>
+      </c>
+      <c r="H7">
+        <v>5.2858000000000001</v>
+      </c>
+      <c r="I7" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="12">
+        <f t="shared" si="0"/>
+        <v>22.756666666666664</v>
+      </c>
+      <c r="M7" s="12" cm="1">
+        <f t="array" ref="M7">STDEV(IF($B$2:$B$28=$K7,D$2:D$28))</f>
+        <v>0.80407296517998628</v>
+      </c>
+      <c r="N7" s="12">
+        <f t="shared" si="1"/>
+        <v>34.136666666666663</v>
+      </c>
+      <c r="O7" s="12" cm="1">
+        <f t="array" ref="O7">STDEV(IF($B$2:$B$28=$K7,E$2:E$28))</f>
+        <v>1.203550303615653</v>
+      </c>
+      <c r="P7" s="13">
+        <f t="shared" si="2"/>
+        <v>585.33333333333337</v>
+      </c>
+      <c r="Q7" s="13" cm="1">
+        <f t="array" ref="Q7">STDEV(IF($B$2:$B$28=$K7,F$2:F$28))</f>
+        <v>21.548395145191982</v>
+      </c>
+      <c r="R7" s="14">
+        <f t="shared" si="3"/>
+        <v>9.729000000000001</v>
+      </c>
+      <c r="S7" s="14" cm="1">
+        <f t="array" ref="S7">STDEV(IF($B$2:$B$28=$K7,G$2:G$28))</f>
+        <v>0.21017373765530237</v>
+      </c>
+      <c r="T7" s="14">
+        <f t="shared" si="4"/>
+        <v>2.3410333333333333</v>
+      </c>
+      <c r="U7" s="14" cm="1">
+        <f t="array" ref="U7">STDEV(IF($B$2:$B$28=$K7,H$2:H$28))</f>
+        <v>0.13050909291437646</v>
+      </c>
+      <c r="W7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.5333512458473111</v>
+      </c>
+      <c r="X7" s="15">
+        <f t="shared" si="6"/>
+        <v>3.5256819752435886</v>
+      </c>
+      <c r="Y7" s="15">
+        <f t="shared" si="7"/>
+        <v>3.6813886922309762</v>
+      </c>
+      <c r="Z7" s="15">
+        <f t="shared" si="8"/>
+        <v>2.1602809914205197</v>
+      </c>
+      <c r="AA7" s="16">
+        <f t="shared" si="9"/>
+        <v>5.5748498347329436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="23">
+        <v>21.89</v>
+      </c>
+      <c r="E8" s="23">
+        <v>32.83</v>
+      </c>
+      <c r="F8">
+        <v>550</v>
+      </c>
+      <c r="G8">
+        <v>7.1710000000000003</v>
+      </c>
+      <c r="H8">
+        <v>3.0522</v>
+      </c>
+      <c r="I8" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" si="0"/>
+        <v>24.900000000000002</v>
+      </c>
+      <c r="M8" s="12" cm="1">
+        <f t="array" ref="M8">STDEV(IF($B$2:$B$28=$K8,D$2:D$28))</f>
+        <v>2.6303421830628801</v>
+      </c>
+      <c r="N8" s="12">
+        <f t="shared" si="1"/>
+        <v>37.353333333333332</v>
+      </c>
+      <c r="O8" s="12" cm="1">
+        <f t="array" ref="O8">STDEV(IF($B$2:$B$28=$K8,E$2:E$28))</f>
+        <v>3.9513331083740981</v>
+      </c>
+      <c r="P8" s="13">
+        <f t="shared" si="2"/>
+        <v>506</v>
+      </c>
+      <c r="Q8" s="13" cm="1">
+        <f t="array" ref="Q8">STDEV(IF($B$2:$B$28=$K8,F$2:F$28))</f>
+        <v>142.20056258679148</v>
+      </c>
+      <c r="R8" s="14">
+        <f t="shared" si="3"/>
+        <v>5.1096666666666666</v>
+      </c>
+      <c r="S8" s="14" cm="1">
+        <f t="array" ref="S8">STDEV(IF($B$2:$B$28=$K8,G$2:G$28))</f>
+        <v>0.13969371257624064</v>
+      </c>
+      <c r="T8" s="14">
+        <f t="shared" si="4"/>
+        <v>4.8789000000000007</v>
+      </c>
+      <c r="U8" s="14" cm="1">
+        <f t="array" ref="U8">STDEV(IF($B$2:$B$28=$K8,H$2:H$28))</f>
+        <v>0.56915728054730164</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="5"/>
+        <v>10.563623225152128</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="6"/>
+        <v>10.578261043300282</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="7"/>
+        <v>28.102877981579343</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="8"/>
+        <v>2.7339104816277766</v>
+      </c>
+      <c r="AA8" s="16">
+        <f t="shared" si="9"/>
+        <v>11.665688588560979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="23">
+        <v>15.16</v>
+      </c>
+      <c r="E9" s="23">
+        <v>22.75</v>
+      </c>
+      <c r="F9">
+        <v>647</v>
+      </c>
+      <c r="G9">
+        <v>9.9870000000000001</v>
+      </c>
+      <c r="H9">
+        <v>1.5183</v>
+      </c>
+      <c r="I9" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" si="0"/>
+        <v>19.386666666666667</v>
+      </c>
+      <c r="M9" s="12" cm="1">
+        <f t="array" ref="M9">STDEV(IF($B$2:$B$28=$K9,D$2:D$28))</f>
+        <v>2.7274591350436999</v>
+      </c>
+      <c r="N9" s="12">
+        <f t="shared" si="1"/>
+        <v>29.076666666666664</v>
+      </c>
+      <c r="O9" s="12" cm="1">
+        <f t="array" ref="O9">STDEV(IF($B$2:$B$28=$K9,E$2:E$28))</f>
+        <v>4.0885245912594925</v>
+      </c>
+      <c r="P9" s="13">
+        <f t="shared" si="2"/>
+        <v>565.66666666666663</v>
+      </c>
+      <c r="Q9" s="13" cm="1">
+        <f t="array" ref="Q9">STDEV(IF($B$2:$B$28=$K9,F$2:F$28))</f>
+        <v>17.7857620959388</v>
+      </c>
+      <c r="R9" s="14">
+        <f t="shared" si="3"/>
+        <v>7.4269999999999996</v>
+      </c>
+      <c r="S9" s="14" cm="1">
+        <f t="array" ref="S9">STDEV(IF($B$2:$B$28=$K9,G$2:G$28))</f>
+        <v>0.22260278524762439</v>
+      </c>
+      <c r="T9" s="14">
+        <f t="shared" si="4"/>
+        <v>2.6173999999999999</v>
+      </c>
+      <c r="U9" s="14" cm="1">
+        <f t="array" ref="U9">STDEV(IF($B$2:$B$28=$K9,H$2:H$28))</f>
+        <v>0.43246915496946137</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" si="5"/>
+        <v>14.068736941422111</v>
+      </c>
+      <c r="X9" s="15">
+        <f t="shared" si="6"/>
+        <v>14.061187405455094</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.1442125095943672</v>
+      </c>
+      <c r="Z9" s="15">
+        <f t="shared" si="8"/>
+        <v>2.9972099804446533</v>
+      </c>
+      <c r="AA9" s="16">
+        <f t="shared" si="9"/>
+        <v>16.52285302091623</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="23">
+        <v>19.72</v>
+      </c>
+      <c r="E10" s="23">
+        <v>29.58</v>
+      </c>
+      <c r="F10">
+        <v>690</v>
+      </c>
+      <c r="G10">
+        <v>9.9730000000000008</v>
+      </c>
+      <c r="H10">
+        <v>1.9770000000000001</v>
+      </c>
+      <c r="I10" s="7">
+        <v>46087</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>16.200000000000003</v>
+      </c>
+      <c r="M10" s="12" cm="1">
+        <f t="array" ref="M10">STDEV(IF($B$2:$B$28=$K10,D$2:D$28))</f>
+        <v>1.0991360243391177</v>
+      </c>
+      <c r="N10" s="12">
+        <f t="shared" si="1"/>
+        <v>24.299999999999997</v>
+      </c>
+      <c r="O10" s="12" cm="1">
+        <f t="array" ref="O10">STDEV(IF($B$2:$B$28=$K10,E$2:E$28))</f>
+        <v>1.6416150584104665</v>
+      </c>
+      <c r="P10" s="13">
+        <f t="shared" si="2"/>
+        <v>673.33333333333337</v>
+      </c>
+      <c r="Q10" s="13" cm="1">
+        <f t="array" ref="Q10">STDEV(IF($B$2:$B$28=$K10,F$2:F$28))</f>
+        <v>34.961884007206095</v>
+      </c>
+      <c r="R10" s="14">
+        <f t="shared" si="3"/>
+        <v>9.8780000000000001</v>
+      </c>
+      <c r="S10" s="14" cm="1">
+        <f t="array" ref="S10">STDEV(IF($B$2:$B$28=$K10,G$2:G$28))</f>
+        <v>0.11781765572273113</v>
+      </c>
+      <c r="T10" s="14">
+        <f t="shared" si="4"/>
+        <v>1.6402666666666665</v>
+      </c>
+      <c r="U10" s="14" cm="1">
+        <f t="array" ref="U10">STDEV(IF($B$2:$B$28=$K10,H$2:H$28))</f>
+        <v>0.11771025160678804</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="5"/>
+        <v>6.7847902736982562</v>
+      </c>
+      <c r="X10" s="15">
+        <f t="shared" si="6"/>
+        <v>6.7556175243229086</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="7"/>
+        <v>5.1923590109712014</v>
+      </c>
+      <c r="Z10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.1927278368367191</v>
+      </c>
+      <c r="AA10" s="16">
+        <f t="shared" si="9"/>
+        <v>7.1762874902528893</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="23">
+        <v>41.48</v>
+      </c>
+      <c r="E11" s="23">
+        <v>62.22</v>
+      </c>
+      <c r="F11">
+        <v>799</v>
+      </c>
+      <c r="G11">
+        <v>11.002000000000001</v>
+      </c>
+      <c r="H11">
+        <v>3.7706</v>
+      </c>
+      <c r="I11" s="7">
+        <v>46138</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="18">
+        <f t="shared" si="0"/>
+        <v>22.683333333333334</v>
+      </c>
+      <c r="M11" s="18" cm="1">
+        <f t="array" ref="M11">STDEV(IF($B$2:$B$28=$K11,D$2:D$28))</f>
+        <v>2.8309068040706071</v>
+      </c>
+      <c r="N11" s="18">
+        <f t="shared" si="1"/>
+        <v>34.026666666666664</v>
+      </c>
+      <c r="O11" s="18" cm="1">
+        <f t="array" ref="O11">STDEV(IF($B$2:$B$28=$K11,E$2:E$28))</f>
+        <v>4.2508391328458064</v>
+      </c>
+      <c r="P11" s="19">
+        <f t="shared" si="2"/>
+        <v>676.66666666666663</v>
+      </c>
+      <c r="Q11" s="19" cm="1">
+        <f t="array" ref="Q11">STDEV(IF($B$2:$B$28=$K11,F$2:F$28))</f>
+        <v>18.147543451754931</v>
+      </c>
+      <c r="R11" s="20">
+        <f t="shared" si="3"/>
+        <v>9.7000000000000011</v>
+      </c>
+      <c r="S11" s="20" cm="1">
+        <f t="array" ref="S11">STDEV(IF($B$2:$B$28=$K11,G$2:G$28))</f>
+        <v>0.34517966336387834</v>
+      </c>
+      <c r="T11" s="20">
+        <f t="shared" si="4"/>
+        <v>2.3468666666666667</v>
+      </c>
+      <c r="U11" s="20" cm="1">
+        <f t="array" ref="U11">STDEV(IF($B$2:$B$28=$K11,H$2:H$28))</f>
+        <v>0.37339874575757737</v>
+      </c>
+      <c r="W11" s="21">
+        <f t="shared" si="5"/>
+        <v>12.480118166365644</v>
+      </c>
+      <c r="X11" s="21">
+        <f t="shared" si="6"/>
+        <v>12.492669865338382</v>
+      </c>
+      <c r="Y11" s="21">
+        <f t="shared" si="7"/>
+        <v>2.6819029731657533</v>
+      </c>
+      <c r="Z11" s="21">
+        <f t="shared" si="8"/>
+        <v>3.5585532305554466</v>
+      </c>
+      <c r="AA11" s="22">
+        <f t="shared" si="9"/>
+        <v>15.910522359922904</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="23">
+        <v>25.42</v>
+      </c>
+      <c r="E12" s="23">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="F12">
+        <v>569</v>
+      </c>
+      <c r="G12">
+        <v>7.51</v>
+      </c>
+      <c r="H12">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="I12" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="23">
+        <v>25.57</v>
+      </c>
+      <c r="E13" s="23">
+        <v>38.36</v>
+      </c>
+      <c r="F13">
+        <v>434</v>
+      </c>
+      <c r="G13">
+        <v>6.7510000000000003</v>
+      </c>
+      <c r="H13">
+        <v>3.7877999999999998</v>
+      </c>
+      <c r="I13" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="23">
+        <v>25.85</v>
+      </c>
+      <c r="E14" s="23">
+        <v>38.770000000000003</v>
+      </c>
+      <c r="F14">
+        <v>701</v>
+      </c>
+      <c r="G14">
+        <v>8.6159999999999997</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="23">
+        <v>21.83</v>
+      </c>
+      <c r="E15" s="23">
+        <v>32.75</v>
+      </c>
+      <c r="F15">
+        <v>593</v>
+      </c>
+      <c r="G15">
+        <v>9.968</v>
+      </c>
+      <c r="H15">
+        <v>2.1903999999999999</v>
+      </c>
+      <c r="I15" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="23">
+        <v>22.07</v>
+      </c>
+      <c r="E16" s="23">
+        <v>33.1</v>
+      </c>
+      <c r="F16">
+        <v>670</v>
+      </c>
+      <c r="G16">
+        <v>5.218</v>
+      </c>
+      <c r="H16">
+        <v>4.2285000000000004</v>
+      </c>
+      <c r="I16" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="23">
+        <v>16.48</v>
+      </c>
+      <c r="E17" s="23">
+        <v>24.72</v>
+      </c>
+      <c r="F17">
+        <v>585</v>
+      </c>
+      <c r="G17">
+        <v>7.5350000000000001</v>
+      </c>
+      <c r="H17">
+        <v>2.1873</v>
+      </c>
+      <c r="I17" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="23">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="E18" s="23">
+        <v>26.02</v>
+      </c>
+      <c r="F18">
+        <v>713</v>
+      </c>
+      <c r="G18">
+        <v>9.8940000000000001</v>
+      </c>
+      <c r="H18">
+        <v>1.7532000000000001</v>
+      </c>
+      <c r="I18" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="23">
+        <v>25.36</v>
+      </c>
+      <c r="E19" s="23">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="F19">
+        <v>656</v>
+      </c>
+      <c r="G19">
+        <v>9.3119999999999994</v>
+      </c>
+      <c r="H19">
+        <v>2.7237</v>
+      </c>
+      <c r="I19" s="7">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="23">
+        <v>41.51</v>
+      </c>
+      <c r="E20" s="23">
+        <v>62.26</v>
+      </c>
+      <c r="F20">
+        <v>816</v>
+      </c>
+      <c r="G20">
+        <v>10.983000000000001</v>
+      </c>
+      <c r="H20">
+        <v>3.7793000000000001</v>
+      </c>
+      <c r="I20" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="23">
+        <v>25.53</v>
+      </c>
+      <c r="E21" s="23">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="F21">
+        <v>584</v>
+      </c>
+      <c r="G21">
+        <v>7.69</v>
+      </c>
+      <c r="H21">
+        <v>3.3203</v>
+      </c>
+      <c r="I21" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="23">
+        <v>18.47</v>
+      </c>
+      <c r="E22" s="23">
+        <v>27.71</v>
+      </c>
+      <c r="F22">
+        <v>450</v>
+      </c>
+      <c r="G22">
+        <v>7.0709999999999997</v>
+      </c>
+      <c r="H22">
+        <v>2.6128</v>
+      </c>
+      <c r="I22" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="23">
+        <v>29.46</v>
+      </c>
+      <c r="E23" s="23">
+        <v>44.19</v>
+      </c>
+      <c r="F23">
+        <v>587</v>
+      </c>
+      <c r="G23">
+        <v>7.6669999999999998</v>
+      </c>
+      <c r="H23">
+        <v>3.8422999999999998</v>
+      </c>
+      <c r="I23" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="23">
+        <v>23.17</v>
+      </c>
+      <c r="E24" s="23">
+        <v>34.75</v>
+      </c>
+      <c r="F24">
+        <v>561</v>
+      </c>
+      <c r="G24">
+        <v>9.5730000000000004</v>
+      </c>
+      <c r="H24">
+        <v>2.4201999999999999</v>
+      </c>
+      <c r="I24" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="23">
+        <v>25.36</v>
+      </c>
+      <c r="E25" s="23">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="F25">
+        <v>417</v>
+      </c>
+      <c r="G25">
+        <v>4.952</v>
+      </c>
+      <c r="H25">
+        <v>5.1223999999999998</v>
+      </c>
+      <c r="I25" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="23">
+        <v>19.79</v>
+      </c>
+      <c r="E26" s="23">
+        <v>29.68</v>
+      </c>
+      <c r="F26">
+        <v>562</v>
+      </c>
+      <c r="G26">
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="H26">
+        <v>2.6126999999999998</v>
+      </c>
+      <c r="I26" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="23">
+        <v>16.09</v>
+      </c>
+      <c r="E27" s="23">
+        <v>24.13</v>
+      </c>
+      <c r="F27">
+        <v>660</v>
+      </c>
+      <c r="G27">
+        <v>9.7530000000000001</v>
+      </c>
+      <c r="H27">
+        <v>1.6493</v>
+      </c>
+      <c r="I27" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="23">
+        <v>22.97</v>
+      </c>
+      <c r="E28" s="23">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="F28">
+        <v>684</v>
+      </c>
+      <c r="G28">
+        <v>9.8149999999999995</v>
+      </c>
+      <c r="H28">
+        <v>2.3399000000000001</v>
+      </c>
+      <c r="I28" s="7">
+        <v>46139</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="W3:AA11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>